--- a/Data Analysis/1_Data/Aggregates/mean_aggregates.xlsx
+++ b/Data Analysis/1_Data/Aggregates/mean_aggregates.xlsx
@@ -393,19 +393,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>88.52704631198192</v>
+        <v>93.01248456999177</v>
       </c>
       <c r="C2">
-        <v>90.331246093394</v>
+        <v>91.85646693257752</v>
       </c>
       <c r="D2">
-        <v>89.27483164983141</v>
+        <v>89.31058178202342</v>
       </c>
       <c r="E2">
-        <v>89.31845476214247</v>
+        <v>82.08537438768387</v>
       </c>
       <c r="F2">
-        <v>89.36289470433745</v>
+        <v>89.06622691806915</v>
       </c>
     </row>
     <row r="3">
@@ -415,19 +415,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>86.96427270214545</v>
+        <v>89.23906330682826</v>
       </c>
       <c r="C3">
-        <v>89.90836305831731</v>
+        <v>93.08160104343249</v>
       </c>
       <c r="D3">
-        <v>90.93319466138031</v>
+        <v>87.31555102903747</v>
       </c>
       <c r="E3">
-        <v>89.91432488837118</v>
+        <v>84.03815843811034</v>
       </c>
       <c r="F3">
-        <v>89.43003882755356</v>
+        <v>88.41859345435213</v>
       </c>
     </row>
     <row r="4">
@@ -437,19 +437,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>83.59996809409957</v>
+        <v>79.38450057258757</v>
       </c>
       <c r="C4">
-        <v>88.05447529446315</v>
+        <v>83.85396551373015</v>
       </c>
       <c r="D4">
-        <v>86.61933417259057</v>
+        <v>78.15849929827294</v>
       </c>
       <c r="E4">
-        <v>77.31249999999996</v>
+        <v>66.58765207651281</v>
       </c>
       <c r="F4">
-        <v>83.89656939028831</v>
+        <v>76.99615436527587</v>
       </c>
     </row>
     <row r="5">
@@ -459,19 +459,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>90.9757902906837</v>
+        <v>77.70412804911547</v>
       </c>
       <c r="C5">
-        <v>93.13181118218368</v>
+        <v>80.61341435778637</v>
       </c>
       <c r="D5">
-        <v>91.70325398097877</v>
+        <v>71.632834110562</v>
       </c>
       <c r="E5">
-        <v>131.5780301624353</v>
+        <v>72.79483166562015</v>
       </c>
       <c r="F5">
-        <v>101.8472214040704</v>
+        <v>75.686302045771</v>
       </c>
     </row>
     <row r="6">
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>90.0610105142645</v>
+        <v>73.49593344258295</v>
       </c>
       <c r="C6">
-        <v>90.63434450798195</v>
+        <v>83.89931277290763</v>
       </c>
       <c r="D6">
-        <v>91.03143600322358</v>
+        <v>68.70260992217997</v>
       </c>
       <c r="E6">
-        <v>122.6550884255091</v>
+        <v>62.7109311230053</v>
       </c>
       <c r="F6">
-        <v>98.59546986274478</v>
+        <v>72.20219681516896</v>
       </c>
     </row>
     <row r="7">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>89.50978800769488</v>
+        <v>89.76616066644301</v>
       </c>
       <c r="C7">
-        <v>91.10879426397439</v>
+        <v>93.88966045256204</v>
       </c>
       <c r="D7">
-        <v>89.27483164983191</v>
+        <v>87.81214892992988</v>
       </c>
       <c r="E7">
-        <v>101.2940780972748</v>
+        <v>87.12717767756918</v>
       </c>
       <c r="F7">
-        <v>92.79687300469401</v>
+        <v>89.64878693162603</v>
       </c>
     </row>
     <row r="8">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>91.75865882860748</v>
+        <v>80.43505971005345</v>
       </c>
       <c r="C8">
-        <v>90.65483246680894</v>
+        <v>83.49577747161716</v>
       </c>
       <c r="D8">
-        <v>90.14350393372661</v>
+        <v>74.13063828700012</v>
       </c>
       <c r="E8">
-        <v>90.88496352392409</v>
+        <v>61.44498127423068</v>
       </c>
       <c r="F8">
-        <v>90.86048968826678</v>
+        <v>74.87661418572536</v>
       </c>
     </row>
     <row r="9">
@@ -547,19 +547,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>88.68617336514895</v>
+        <v>82.36274843971708</v>
       </c>
       <c r="C9">
-        <v>90.41498079331215</v>
+        <v>82.77803886852247</v>
       </c>
       <c r="D9">
-        <v>90.00629540566011</v>
+        <v>79.07658431192023</v>
       </c>
       <c r="E9">
-        <v>87.55248694827759</v>
+        <v>66.22142113951092</v>
       </c>
       <c r="F9">
-        <v>89.1649841280997</v>
+        <v>77.60969818991768</v>
       </c>
     </row>
     <row r="10">
@@ -569,19 +569,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>91.86029155679368</v>
+        <v>91.33584949321595</v>
       </c>
       <c r="C10">
-        <v>94.38811799899236</v>
+        <v>93.38279276060887</v>
       </c>
       <c r="D10">
-        <v>93.33007607535735</v>
+        <v>87.90097949022423</v>
       </c>
       <c r="E10">
-        <v>90.62892663519692</v>
+        <v>80.25913825375763</v>
       </c>
       <c r="F10">
-        <v>92.55185306658508</v>
+        <v>88.21968999945167</v>
       </c>
     </row>
     <row r="11">
@@ -591,19 +591,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>91.3466838435113</v>
+        <v>81.6590782110936</v>
       </c>
       <c r="C11">
-        <v>90.5334214336803</v>
+        <v>90.05264660708254</v>
       </c>
       <c r="D11">
-        <v>91.31067182929598</v>
+        <v>72.83986492022359</v>
       </c>
       <c r="E11">
-        <v>90.34639689208991</v>
+        <v>58.09996674677196</v>
       </c>
       <c r="F11">
-        <v>90.88429349964437</v>
+        <v>75.66288912129292</v>
       </c>
     </row>
     <row r="12">
@@ -613,19 +613,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>91.67118389957906</v>
+        <v>74.69791586005874</v>
       </c>
       <c r="C12">
-        <v>90.68322649572637</v>
+        <v>79.53093573317159</v>
       </c>
       <c r="D12">
-        <v>91.38687719644008</v>
+        <v>63.26905561297372</v>
       </c>
       <c r="E12">
-        <v>91.06199186991874</v>
+        <v>70.22196927082189</v>
       </c>
       <c r="F12">
-        <v>91.20081986541607</v>
+        <v>71.92996911925648</v>
       </c>
     </row>
     <row r="13">
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>84.14482073207287</v>
+        <v>85.51356221262175</v>
       </c>
       <c r="C13">
-        <v>85.03264726284237</v>
+        <v>93.82500187931764</v>
       </c>
       <c r="D13">
-        <v>85.79822204781463</v>
+        <v>80.85556440424445</v>
       </c>
       <c r="E13">
-        <v>84.33768656716414</v>
+        <v>65.09451149378306</v>
       </c>
       <c r="F13">
-        <v>84.82834415247351</v>
+        <v>81.32215999749172</v>
       </c>
     </row>
     <row r="14">
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>92.83716832504147</v>
+        <v>73.33086064413033</v>
       </c>
       <c r="C14">
-        <v>94.44621904238095</v>
+        <v>75.84277056727844</v>
       </c>
       <c r="D14">
-        <v>95.84177197609773</v>
+        <v>60.29006675571636</v>
       </c>
       <c r="E14">
-        <v>136.5310770090778</v>
+        <v>68.75179228363662</v>
       </c>
       <c r="F14">
-        <v>104.9140590881495</v>
+        <v>69.55387256269043</v>
       </c>
     </row>
     <row r="15">
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>90.33840429344073</v>
+        <v>82.06243418740236</v>
       </c>
       <c r="C15">
-        <v>92.2765805992358</v>
+        <v>90.76102798477611</v>
       </c>
       <c r="D15">
-        <v>95.16692311820277</v>
+        <v>70.48474030715613</v>
       </c>
       <c r="E15">
-        <v>88.49249820965052</v>
+        <v>75.56727765308348</v>
       </c>
       <c r="F15">
-        <v>91.56860155513246</v>
+        <v>79.71887003310452</v>
       </c>
     </row>
     <row r="16">
@@ -701,19 +701,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>90.61132599199161</v>
+        <v>78.25808054478078</v>
       </c>
       <c r="C16">
-        <v>92.68039869313611</v>
+        <v>86.07639561406238</v>
       </c>
       <c r="D16">
-        <v>94.04629153085159</v>
+        <v>67.76155792522397</v>
       </c>
       <c r="E16">
-        <v>91.15722852773075</v>
+        <v>72.57229819576375</v>
       </c>
       <c r="F16">
-        <v>92.12381118592751</v>
+        <v>76.16708306995773</v>
       </c>
     </row>
     <row r="17">
@@ -723,19 +723,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>91.53025855349389</v>
+        <v>81.08714738479897</v>
       </c>
       <c r="C17">
-        <v>92.41877077223562</v>
+        <v>87.00421345953923</v>
       </c>
       <c r="D17">
-        <v>93.69924737571755</v>
+        <v>77.27419697290156</v>
       </c>
       <c r="E17">
-        <v>99.76456417407913</v>
+        <v>61.33233312294647</v>
       </c>
       <c r="F17">
-        <v>94.35321021888154</v>
+        <v>76.67447273504655</v>
       </c>
     </row>
     <row r="18">
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>85.72614317077044</v>
+        <v>85.04347816239522</v>
       </c>
       <c r="C18">
-        <v>91.28561705204254</v>
+        <v>92.11632128700984</v>
       </c>
       <c r="D18">
-        <v>97.14634389104837</v>
+        <v>54.98779394950725</v>
       </c>
       <c r="E18">
-        <v>88.11498379315576</v>
+        <v>82.4195140840517</v>
       </c>
       <c r="F18">
-        <v>90.56827197675427</v>
+        <v>78.641776870741</v>
       </c>
     </row>
     <row r="19">
@@ -767,19 +767,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>89.06921825601047</v>
+        <v>86.35859071724538</v>
       </c>
       <c r="C19">
-        <v>88.70381512660612</v>
+        <v>95.21625530095518</v>
       </c>
       <c r="D19">
-        <v>82.5942656765673</v>
+        <v>84.75473407010391</v>
       </c>
       <c r="E19">
-        <v>89.5417053960297</v>
+        <v>79.66412214225799</v>
       </c>
       <c r="F19">
-        <v>87.47725111380339</v>
+        <v>86.49842555764062</v>
       </c>
     </row>
     <row r="20">
@@ -789,19 +789,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>89.46610906971053</v>
+        <v>80.22119980799626</v>
       </c>
       <c r="C20">
-        <v>95.12305712100381</v>
+        <v>86.83103000767413</v>
       </c>
       <c r="D20">
-        <v>93.79402118949004</v>
+        <v>71.06840817194764</v>
       </c>
       <c r="E20">
-        <v>90.26426116423582</v>
+        <v>71.70088553349899</v>
       </c>
       <c r="F20">
-        <v>92.16186213611005</v>
+        <v>77.45538088027925</v>
       </c>
     </row>
     <row r="21">
@@ -811,19 +811,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>90.09065826468505</v>
+        <v>92.8920144296831</v>
       </c>
       <c r="C21">
-        <v>92.99394555589906</v>
+        <v>96.51070451899095</v>
       </c>
       <c r="D21">
-        <v>94.12085469651534</v>
+        <v>87.89858562517507</v>
       </c>
       <c r="E21">
-        <v>87.76430348258714</v>
+        <v>89.88318102504942</v>
       </c>
       <c r="F21">
-        <v>91.24244049992164</v>
+        <v>91.79612139972464</v>
       </c>
     </row>
     <row r="22">
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>90.54311056105604</v>
+        <v>92.63729475231575</v>
       </c>
       <c r="C22">
-        <v>90.26355684973014</v>
+        <v>91.86171422225493</v>
       </c>
       <c r="D22">
-        <v>93.18997524752439</v>
+        <v>89.15060889267784</v>
       </c>
       <c r="E22">
-        <v>94.33185330245992</v>
+        <v>80.67632678528777</v>
       </c>
       <c r="F22">
-        <v>92.08212399019263</v>
+        <v>88.58148616313407</v>
       </c>
     </row>
     <row r="23">
@@ -855,19 +855,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>92.9906286206067</v>
+        <v>87.09476246426441</v>
       </c>
       <c r="C23">
-        <v>93.66757052728089</v>
+        <v>89.51432485355815</v>
       </c>
       <c r="D23">
-        <v>93.82587268909924</v>
+        <v>79.97847991839377</v>
       </c>
       <c r="E23">
-        <v>85.86159940714711</v>
+        <v>82.58658112658624</v>
       </c>
       <c r="F23">
-        <v>91.58641781103348</v>
+        <v>84.79353709070064</v>
       </c>
     </row>
     <row r="24">
@@ -877,19 +877,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>92.56983550169288</v>
+        <v>94.72684871681533</v>
       </c>
       <c r="C24">
-        <v>85.80981638443536</v>
+        <v>94.83542297602357</v>
       </c>
       <c r="D24">
-        <v>92.92379405444753</v>
+        <v>87.91004927773876</v>
       </c>
       <c r="E24">
-        <v>92.435494098137</v>
+        <v>81.32630320238293</v>
       </c>
       <c r="F24">
-        <v>90.93473500967819</v>
+        <v>89.69965604324014</v>
       </c>
     </row>
     <row r="25">
@@ -899,19 +899,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>93.64924531319731</v>
+        <v>67.28152804079583</v>
       </c>
       <c r="C25">
-        <v>94.57927885901181</v>
+        <v>73.56129883008599</v>
       </c>
       <c r="D25">
-        <v>95.34896248422507</v>
+        <v>63.77266104720584</v>
       </c>
       <c r="E25">
-        <v>93.86035715099065</v>
+        <v>46.77266627177513</v>
       </c>
       <c r="F25">
-        <v>94.35946095185621</v>
+        <v>62.8470385474657</v>
       </c>
     </row>
     <row r="26">
@@ -921,19 +921,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>87.44150666785804</v>
+        <v>79.20994005244516</v>
       </c>
       <c r="C26">
-        <v>94.63811050327854</v>
+        <v>80.37713769636889</v>
       </c>
       <c r="D26">
-        <v>92.91476900164821</v>
+        <v>76.79137456111529</v>
       </c>
       <c r="E26">
-        <v>93.90139562710296</v>
+        <v>63.97541833013832</v>
       </c>
       <c r="F26">
-        <v>92.22394544997194</v>
+        <v>75.08846766001692</v>
       </c>
     </row>
     <row r="27">
@@ -943,16 +943,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>89.81753467038259</v>
+        <v>87.94211538188448</v>
+      </c>
+      <c r="C27">
+        <v>92.52671411342173</v>
       </c>
       <c r="D27">
-        <v>92.46170033670079</v>
+        <v>85.34693503441214</v>
       </c>
       <c r="E27">
-        <v>91.98776948590367</v>
+        <v>74.61337774721326</v>
       </c>
       <c r="F27">
-        <v>91.42233483099568</v>
+        <v>85.1072855692329</v>
       </c>
     </row>
     <row r="28">
@@ -962,19 +965,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>93.16730059460367</v>
+        <v>78.60623867414972</v>
       </c>
       <c r="C28">
-        <v>94.49680622979476</v>
+        <v>86.81592962449845</v>
       </c>
       <c r="D28">
-        <v>94.32761364005869</v>
+        <v>79.09703869111426</v>
       </c>
       <c r="E28">
-        <v>91.49685794728906</v>
+        <v>71.80616276502157</v>
       </c>
       <c r="F28">
-        <v>93.37214460293654</v>
+        <v>79.081342438696</v>
       </c>
     </row>
     <row r="29">
@@ -984,19 +987,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>89.28793479724895</v>
+        <v>90.23541532623952</v>
       </c>
       <c r="C29">
-        <v>93.10139576298512</v>
+        <v>93.19005166119554</v>
       </c>
       <c r="D29">
-        <v>92.61536280105378</v>
+        <v>80.60139977284035</v>
       </c>
       <c r="E29">
-        <v>88.3847346134783</v>
+        <v>88.77346470201267</v>
       </c>
       <c r="F29">
-        <v>90.84735699369153</v>
+        <v>88.20008286557203</v>
       </c>
     </row>
     <row r="30">
@@ -1006,19 +1009,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>90.60894295529171</v>
+        <v>91.28364300331502</v>
       </c>
       <c r="C30">
-        <v>95.47442892552823</v>
+        <v>92.88118402007422</v>
       </c>
       <c r="D30">
-        <v>93.53798961969113</v>
+        <v>92.04572562706646</v>
       </c>
       <c r="E30">
-        <v>86.62932985298568</v>
+        <v>89.5727374866498</v>
       </c>
       <c r="F30">
-        <v>91.56267283837418</v>
+        <v>91.44582253427637</v>
       </c>
     </row>
     <row r="31">
@@ -1028,19 +1031,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>92.42739898989879</v>
+        <v>90.18068935509595</v>
       </c>
       <c r="C31">
-        <v>92.03057705787576</v>
+        <v>95.69653686486595</v>
       </c>
       <c r="D31">
-        <v>92.98892911648585</v>
+        <v>91.95804825023805</v>
       </c>
       <c r="E31">
-        <v>94.46653064627714</v>
+        <v>81.34573955774218</v>
       </c>
       <c r="F31">
-        <v>92.97835895263438</v>
+        <v>89.79525350698553</v>
       </c>
     </row>
     <row r="32">
@@ -1050,19 +1053,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>90.43918350168346</v>
+        <v>87.03966451469306</v>
       </c>
       <c r="C32">
-        <v>92.53043807706415</v>
+        <v>91.81027046216387</v>
       </c>
       <c r="D32">
-        <v>94.50553095510556</v>
+        <v>81.05528042490798</v>
       </c>
       <c r="E32">
-        <v>88.59160519250861</v>
+        <v>82.11794370706778</v>
       </c>
       <c r="F32">
-        <v>91.51668943159044</v>
+        <v>85.50578977720818</v>
       </c>
     </row>
     <row r="33">
@@ -1072,19 +1075,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>94.63062480303857</v>
+        <v>88.00535105626322</v>
       </c>
       <c r="C33">
-        <v>90.21705971541502</v>
+        <v>93.34907408976737</v>
       </c>
       <c r="D33">
-        <v>94.05268282670552</v>
+        <v>80.05776593474327</v>
       </c>
       <c r="E33">
-        <v>92.94208098573667</v>
+        <v>82.14688092718039</v>
       </c>
       <c r="F33">
-        <v>92.96061208272394</v>
+        <v>85.88976800198856</v>
       </c>
     </row>
     <row r="34">
@@ -1094,19 +1097,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>88.75347275632829</v>
+        <v>68.93229334481777</v>
       </c>
       <c r="C34">
-        <v>93.13068320720953</v>
+        <v>84.00816040985477</v>
       </c>
       <c r="D34">
-        <v>93.66529292523126</v>
+        <v>62.36555832243543</v>
       </c>
       <c r="E34">
-        <v>62.58891321824475</v>
+        <v>535.3277706119746</v>
       </c>
       <c r="F34">
-        <v>84.53459052675346</v>
+        <v>187.6584456722707</v>
       </c>
     </row>
     <row r="35">
@@ -1116,19 +1119,19 @@
         </is>
       </c>
       <c r="B35">
-        <v>88.37171180353347</v>
+        <v>89.85966947950421</v>
       </c>
       <c r="C35">
-        <v>93.19837214714319</v>
+        <v>89.94708590230563</v>
       </c>
       <c r="D35">
-        <v>94.40664197337968</v>
+        <v>87.74016380206895</v>
       </c>
       <c r="E35">
-        <v>92.10081423601642</v>
+        <v>81.45035709608518</v>
       </c>
       <c r="F35">
-        <v>92.01938504001819</v>
+        <v>87.24931906999099</v>
       </c>
     </row>
     <row r="36">
@@ -1138,19 +1141,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>92.40174630208111</v>
+        <v>85.60157727236876</v>
       </c>
       <c r="C36">
-        <v>92.91066404135103</v>
+        <v>92.09941673393742</v>
       </c>
       <c r="D36">
-        <v>95.81861525704812</v>
+        <v>83.36368704065673</v>
       </c>
       <c r="E36">
-        <v>90.62960636515932</v>
+        <v>76.07326426982718</v>
       </c>
       <c r="F36">
-        <v>92.94015799140989</v>
+        <v>84.28448632919752</v>
       </c>
     </row>
     <row r="37">
@@ -1160,19 +1163,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>90.67058925323047</v>
+        <v>91.80182009111071</v>
       </c>
       <c r="C37">
-        <v>91.17463101171155</v>
+        <v>95.20228923158454</v>
       </c>
       <c r="D37">
-        <v>93.48026186129185</v>
+        <v>82.42344418527232</v>
       </c>
       <c r="E37">
-        <v>74.91739872516683</v>
+        <v>68.44811404031536</v>
       </c>
       <c r="F37">
-        <v>87.56072021285019</v>
+        <v>84.46891688707073</v>
       </c>
     </row>
     <row r="38">
@@ -1182,16 +1185,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>94.53382838283831</v>
+        <v>82.54219351014117</v>
+      </c>
+      <c r="C38">
+        <v>84.66848750652737</v>
       </c>
       <c r="D38">
-        <v>94.89493641279357</v>
+        <v>79.73502237736238</v>
       </c>
       <c r="E38">
-        <v>91.46785014322339</v>
+        <v>73.60475891698815</v>
       </c>
       <c r="F38">
-        <v>93.63220497961842</v>
+        <v>80.13761557775477</v>
       </c>
     </row>
     <row r="39">
@@ -1201,16 +1207,19 @@
         </is>
       </c>
       <c r="B39">
-        <v>92.65144428873191</v>
+        <v>85.51866041342365</v>
+      </c>
+      <c r="C39">
+        <v>91.49605755036089</v>
       </c>
       <c r="D39">
-        <v>95.48994252873568</v>
+        <v>83.60823163965453</v>
       </c>
       <c r="E39">
-        <v>89.69657590759061</v>
+        <v>80.40800779490188</v>
       </c>
       <c r="F39">
-        <v>92.61265424168607</v>
+        <v>85.25773934958524</v>
       </c>
     </row>
     <row r="40">
@@ -1220,19 +1229,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>92.84649873569455</v>
+        <v>93.56534954885821</v>
       </c>
       <c r="C40">
-        <v>92.87509949212661</v>
+        <v>92.84067771193726</v>
       </c>
       <c r="D40">
-        <v>94.44193175536456</v>
+        <v>85.99067069411666</v>
       </c>
       <c r="E40">
-        <v>85.70094417077198</v>
+        <v>93.20083081575166</v>
       </c>
       <c r="F40">
-        <v>91.46611853848943</v>
+        <v>91.39938219266594</v>
       </c>
     </row>
     <row r="41">
@@ -1242,19 +1251,19 @@
         </is>
       </c>
       <c r="B41">
-        <v>91.26530854227562</v>
+        <v>92.83284952124363</v>
       </c>
       <c r="C41">
-        <v>93.56671288226754</v>
+        <v>96.35464948078942</v>
       </c>
       <c r="D41">
-        <v>90.07121998964612</v>
+        <v>85.3563192926302</v>
       </c>
       <c r="E41">
-        <v>89.169699445435</v>
+        <v>86.78155523354744</v>
       </c>
       <c r="F41">
-        <v>91.01823521490607</v>
+        <v>90.33134338205267</v>
       </c>
     </row>
     <row r="42">
@@ -1264,19 +1273,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>88.82958438222413</v>
+        <v>72.12356763406567</v>
       </c>
       <c r="C42">
-        <v>88.56989296531235</v>
+        <v>92.01772519250767</v>
       </c>
       <c r="D42">
-        <v>92.91779556650276</v>
+        <v>62.81230232449741</v>
       </c>
       <c r="E42">
-        <v>91.62331649831675</v>
+        <v>67.69082109540875</v>
       </c>
       <c r="F42">
-        <v>90.48514735308899</v>
+        <v>73.66110406161988</v>
       </c>
     </row>
     <row r="43">
@@ -1286,19 +1295,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>93.12791295549957</v>
+        <v>68.25289691588546</v>
       </c>
       <c r="C43">
-        <v>91.96593627935414</v>
+        <v>84.41774506187849</v>
       </c>
       <c r="D43">
-        <v>95.97543261336354</v>
+        <v>73.86233178823582</v>
       </c>
       <c r="E43">
-        <v>88.28133175215854</v>
+        <v>69.894930116219</v>
       </c>
       <c r="F43">
-        <v>92.33765340009394</v>
+        <v>74.10697597055469</v>
       </c>
     </row>
     <row r="44">
@@ -1308,19 +1317,19 @@
         </is>
       </c>
       <c r="B44">
-        <v>91.14485595725752</v>
+        <v>67.75960871741746</v>
       </c>
       <c r="C44">
-        <v>94.72259439817542</v>
+        <v>84.90881233496653</v>
       </c>
       <c r="D44">
-        <v>90.62909029476623</v>
+        <v>78.80573929689854</v>
       </c>
       <c r="E44">
-        <v>94.36502686598718</v>
+        <v>64.62654842424627</v>
       </c>
       <c r="F44">
-        <v>92.71539187904659</v>
+        <v>74.02517719338221</v>
       </c>
     </row>
     <row r="45">
@@ -1330,19 +1339,19 @@
         </is>
       </c>
       <c r="B45">
-        <v>93.5717322180889</v>
+        <v>80.34712453251548</v>
       </c>
       <c r="C45">
-        <v>95.08354562862768</v>
+        <v>94.16819666380239</v>
       </c>
       <c r="D45">
-        <v>90.47842846952648</v>
+        <v>83.84345164645339</v>
       </c>
       <c r="E45">
-        <v>88.82939469320056</v>
+        <v>71.51922269055619</v>
       </c>
       <c r="F45">
-        <v>91.9907752523609</v>
+        <v>82.46949888333187</v>
       </c>
     </row>
     <row r="46">
@@ -1352,19 +1361,19 @@
         </is>
       </c>
       <c r="B46">
-        <v>94.93435075034996</v>
+        <v>84.77512605263074</v>
       </c>
       <c r="C46">
-        <v>94.92224281861576</v>
+        <v>94.72225840518378</v>
       </c>
       <c r="D46">
-        <v>96.32803506974922</v>
+        <v>89.3503560244036</v>
       </c>
       <c r="E46">
-        <v>90.10658619342286</v>
+        <v>81.87461536186075</v>
       </c>
       <c r="F46">
-        <v>94.07280370803446</v>
+        <v>87.68058896101971</v>
       </c>
     </row>
     <row r="47">
@@ -1374,19 +1383,19 @@
         </is>
       </c>
       <c r="B47">
-        <v>91.01524722524029</v>
+        <v>71.66311767374461</v>
       </c>
       <c r="C47">
-        <v>94.96103708731516</v>
+        <v>90.66693737575137</v>
       </c>
       <c r="D47">
-        <v>94.57005200557373</v>
+        <v>79.68216705466554</v>
       </c>
       <c r="E47">
-        <v>93.23692871698239</v>
+        <v>74.63576383475589</v>
       </c>
       <c r="F47">
-        <v>93.4458162587779</v>
+        <v>79.16199648472936</v>
       </c>
     </row>
     <row r="48">
@@ -1396,19 +1405,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>92.16901604127297</v>
+        <v>88.80318241092375</v>
       </c>
       <c r="C48">
-        <v>88.50846329417374</v>
+        <v>95.25462453064358</v>
       </c>
       <c r="D48">
-        <v>94.37495254578106</v>
+        <v>90.42271505426186</v>
       </c>
       <c r="E48">
-        <v>92.79003267973863</v>
+        <v>75.3823168574428</v>
       </c>
       <c r="F48">
-        <v>91.9606161402416</v>
+        <v>87.46570971331801</v>
       </c>
     </row>
     <row r="49">
@@ -1418,19 +1427,19 @@
         </is>
       </c>
       <c r="B49">
-        <v>94.99706294225052</v>
+        <v>63.12249067659924</v>
       </c>
       <c r="C49">
-        <v>95.02665442017751</v>
+        <v>77.89012302780702</v>
       </c>
       <c r="D49">
-        <v>93.1131795983657</v>
+        <v>66.56292156804228</v>
       </c>
       <c r="E49">
-        <v>93.80961766991211</v>
+        <v>54.97369422524827</v>
       </c>
       <c r="F49">
-        <v>94.23662865767646</v>
+        <v>65.63730737442421</v>
       </c>
     </row>
     <row r="50">
@@ -1440,19 +1449,19 @@
         </is>
       </c>
       <c r="B50">
-        <v>91.62131863945947</v>
+        <v>86.66379868947546</v>
       </c>
       <c r="C50">
-        <v>94.65092232389456</v>
+        <v>97.17286503423196</v>
       </c>
       <c r="D50">
-        <v>93.09695837392542</v>
+        <v>92.97795410309318</v>
       </c>
       <c r="E50">
-        <v>90.84443535442256</v>
+        <v>90.69655227623812</v>
       </c>
       <c r="F50">
-        <v>92.5534086729255</v>
+        <v>91.87779252575967</v>
       </c>
     </row>
     <row r="51">
@@ -1462,19 +1471,19 @@
         </is>
       </c>
       <c r="B51">
-        <v>89.5189392035649</v>
+        <v>93.69547617961024</v>
       </c>
       <c r="C51">
-        <v>91.37851297296508</v>
+        <v>97.68562843375862</v>
       </c>
       <c r="D51">
-        <v>92.24739902906136</v>
+        <v>92.87461176891681</v>
       </c>
       <c r="E51">
-        <v>89.44014382402732</v>
+        <v>93.62155317155869</v>
       </c>
       <c r="F51">
-        <v>90.64624875740466</v>
+        <v>94.46931738846109</v>
       </c>
     </row>
     <row r="52">
@@ -1484,19 +1493,19 @@
         </is>
       </c>
       <c r="B52">
-        <v>89.34130222067418</v>
+        <v>73.78221228001905</v>
       </c>
       <c r="C52">
-        <v>93.15517000776913</v>
+        <v>90.5794508806196</v>
       </c>
       <c r="D52">
-        <v>89.56526130033626</v>
+        <v>82.52580077623963</v>
       </c>
       <c r="E52">
-        <v>84.41595836412935</v>
+        <v>87.36116476006562</v>
       </c>
       <c r="F52">
-        <v>89.11942297322723</v>
+        <v>83.56215717423598</v>
       </c>
     </row>
     <row r="53">
@@ -1506,19 +1515,19 @@
         </is>
       </c>
       <c r="B53">
-        <v>90.3720306181109</v>
+        <v>85.37462946723386</v>
       </c>
       <c r="C53">
-        <v>93.89541626411966</v>
+        <v>94.90627595418279</v>
       </c>
       <c r="D53">
-        <v>93.2861675126902</v>
+        <v>85.09704142676999</v>
       </c>
       <c r="E53">
-        <v>61.49749609530878</v>
+        <v>499.2671504360211</v>
       </c>
       <c r="F53">
-        <v>84.76277762255738</v>
+        <v>191.1612743210519</v>
       </c>
     </row>
     <row r="54">
@@ -1528,19 +1537,19 @@
         </is>
       </c>
       <c r="B54">
-        <v>92.81332339992088</v>
+        <v>86.62894747199034</v>
       </c>
       <c r="C54">
-        <v>87.81820716809959</v>
+        <v>94.77405842685368</v>
       </c>
       <c r="D54">
-        <v>94.53400932330244</v>
+        <v>87.43021783363868</v>
       </c>
       <c r="E54">
-        <v>91.04771004496696</v>
+        <v>87.0685284562723</v>
       </c>
       <c r="F54">
-        <v>91.55331248407246</v>
+        <v>88.97543804718876</v>
       </c>
     </row>
     <row r="55">
@@ -1550,19 +1559,19 @@
         </is>
       </c>
       <c r="B55">
-        <v>91.23853418006539</v>
+        <v>71.59201895184468</v>
       </c>
       <c r="C55">
-        <v>89.23489504050895</v>
+        <v>86.88809230825434</v>
       </c>
       <c r="D55">
-        <v>94.49152185626747</v>
+        <v>79.75859602068137</v>
       </c>
       <c r="E55">
-        <v>84.1616673982671</v>
+        <v>80.03037067958917</v>
       </c>
       <c r="F55">
-        <v>89.78165461877722</v>
+        <v>79.56726949009239</v>
       </c>
     </row>
     <row r="56">
@@ -1572,19 +1581,19 @@
         </is>
       </c>
       <c r="B56">
-        <v>90.49699389355202</v>
+        <v>61.91987466807181</v>
       </c>
       <c r="C56">
-        <v>92.65178020983024</v>
+        <v>79.85725810014482</v>
       </c>
       <c r="D56">
-        <v>90.10885247707135</v>
+        <v>59.88619215390431</v>
       </c>
       <c r="E56">
-        <v>93.10404342239637</v>
+        <v>58.31585700406149</v>
       </c>
       <c r="F56">
-        <v>91.59041750071249</v>
+        <v>64.99479548154561</v>
       </c>
     </row>
     <row r="57">
@@ -1594,19 +1603,19 @@
         </is>
       </c>
       <c r="B57">
-        <v>93.72785960174379</v>
+        <v>80.63505101146414</v>
       </c>
       <c r="C57">
-        <v>93.83965550240696</v>
+        <v>88.1503506802281</v>
       </c>
       <c r="D57">
-        <v>89.78672609176328</v>
+        <v>85.88053126491623</v>
       </c>
       <c r="E57">
-        <v>90.74931866403273</v>
+        <v>68.58719180004974</v>
       </c>
       <c r="F57">
-        <v>92.02588996498669</v>
+        <v>80.81328118916456</v>
       </c>
     </row>
     <row r="58">
@@ -1616,19 +1625,19 @@
         </is>
       </c>
       <c r="B58">
-        <v>94.30446567666722</v>
+        <v>89.5611963664156</v>
       </c>
       <c r="C58">
-        <v>90.94078694551791</v>
+        <v>93.91580607224655</v>
       </c>
       <c r="D58">
-        <v>95.56233062330648</v>
+        <v>84.95020457637592</v>
       </c>
       <c r="E58">
-        <v>94.17543352241617</v>
+        <v>68.71693183831331</v>
       </c>
       <c r="F58">
-        <v>93.74575419197694</v>
+        <v>84.28603471333784</v>
       </c>
     </row>
     <row r="59">
@@ -1638,19 +1647,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>94.52679181095419</v>
+        <v>70.44222318113925</v>
       </c>
       <c r="C59">
-        <v>92.58076053910845</v>
+        <v>86.04918909655608</v>
       </c>
       <c r="D59">
-        <v>91.65843729426548</v>
+        <v>74.58169032050336</v>
       </c>
       <c r="E59">
-        <v>91.08026938478338</v>
+        <v>72.71809813220172</v>
       </c>
       <c r="F59">
-        <v>92.46156475727787</v>
+        <v>75.9478001826001</v>
       </c>
     </row>
     <row r="60">
@@ -1660,19 +1669,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>89.69135591322994</v>
+        <v>90.71279536603899</v>
       </c>
       <c r="C60">
-        <v>91.56470028134886</v>
+        <v>96.68437041140264</v>
       </c>
       <c r="D60">
-        <v>89.34923754666947</v>
+        <v>95.41303142259657</v>
       </c>
       <c r="E60">
-        <v>89.95866283916129</v>
+        <v>84.86583535015939</v>
       </c>
       <c r="F60">
-        <v>90.1409891451024</v>
+        <v>91.9190081375494</v>
       </c>
     </row>
     <row r="61">
@@ -1682,19 +1691,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>89.42618714152309</v>
+        <v>87.85408793102306</v>
       </c>
       <c r="C61">
-        <v>93.77072603788493</v>
+        <v>95.66832587893968</v>
       </c>
       <c r="D61">
-        <v>88.89680884791737</v>
+        <v>94.07047539894613</v>
       </c>
       <c r="E61">
-        <v>89.21646341463419</v>
+        <v>88.1355701066135</v>
       </c>
       <c r="F61">
-        <v>90.32754636048989</v>
+        <v>91.4321148288806</v>
       </c>
     </row>
     <row r="62">
@@ -1704,19 +1713,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>87.79542838154396</v>
+        <v>90.92992743566791</v>
       </c>
       <c r="C62">
-        <v>92.89134043426712</v>
+        <v>97.81696401280955</v>
       </c>
       <c r="D62">
-        <v>89.27148872522741</v>
+        <v>95.20543491168719</v>
       </c>
       <c r="E62">
-        <v>89.73836565518182</v>
+        <v>88.94042972658768</v>
       </c>
       <c r="F62">
-        <v>89.92415579905509</v>
+        <v>93.22318902168809</v>
       </c>
     </row>
     <row r="63">
@@ -1726,19 +1735,19 @@
         </is>
       </c>
       <c r="B63">
-        <v>78.48186367474253</v>
+        <v>121.6426254491709</v>
       </c>
       <c r="C63">
-        <v>92.78866476816749</v>
+        <v>97.96578846454715</v>
       </c>
       <c r="D63">
-        <v>91.79166666666653</v>
+        <v>94.72310225195521</v>
       </c>
       <c r="E63">
-        <v>85.43047721877852</v>
+        <v>94.62862305636656</v>
       </c>
       <c r="F63">
-        <v>87.12316808208877</v>
+        <v>102.2400348055099</v>
       </c>
     </row>
     <row r="64">
@@ -1748,19 +1757,19 @@
         </is>
       </c>
       <c r="B64">
-        <v>92.05768315646701</v>
+        <v>89.3097706277216</v>
       </c>
       <c r="C64">
-        <v>89.90514730641064</v>
+        <v>96.16304990005881</v>
       </c>
       <c r="D64">
-        <v>83.47095063301354</v>
+        <v>96.8312472837888</v>
       </c>
       <c r="E64">
-        <v>87.92594075584033</v>
+        <v>93.04655588727415</v>
       </c>
       <c r="F64">
-        <v>88.33993046293288</v>
+        <v>93.83765592471084</v>
       </c>
     </row>
     <row r="65">
@@ -1770,19 +1779,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>88.36382369201409</v>
+        <v>78.24948254041324</v>
       </c>
       <c r="C65">
-        <v>93.25519847736383</v>
+        <v>96.14893884769133</v>
       </c>
       <c r="D65">
-        <v>87.65711382113845</v>
+        <v>95.02568235298695</v>
       </c>
       <c r="E65">
-        <v>88.48721261978062</v>
+        <v>82.50234585023425</v>
       </c>
       <c r="F65">
-        <v>89.44083715257425</v>
+        <v>87.98161239783144</v>
       </c>
     </row>
     <row r="66">
@@ -1792,19 +1801,19 @@
         </is>
       </c>
       <c r="B66">
-        <v>94.43453891708947</v>
+        <v>78.10706440388719</v>
       </c>
       <c r="C66">
-        <v>89.49750546330762</v>
+        <v>92.45196196462184</v>
       </c>
       <c r="D66">
-        <v>90.26469552443052</v>
+        <v>89.59396009466117</v>
       </c>
       <c r="E66">
-        <v>90.04300286335123</v>
+        <v>88.08467732857757</v>
       </c>
       <c r="F66">
-        <v>91.05993569204472</v>
+        <v>87.05941594793694</v>
       </c>
     </row>
     <row r="67">
@@ -1814,19 +1823,19 @@
         </is>
       </c>
       <c r="B67">
-        <v>93.03722202049035</v>
+        <v>63.82617044238492</v>
       </c>
       <c r="C67">
-        <v>93.91802430135526</v>
+        <v>85.58816124913834</v>
       </c>
       <c r="D67">
-        <v>94.9221487292552</v>
+        <v>73.34394169053471</v>
       </c>
       <c r="E67">
-        <v>79.45839400116458</v>
+        <v>73.18057206249799</v>
       </c>
       <c r="F67">
-        <v>90.33394726306635</v>
+        <v>73.98471136113899</v>
       </c>
     </row>
     <row r="68">
@@ -1836,19 +1845,19 @@
         </is>
       </c>
       <c r="B68">
-        <v>93.32773631840814</v>
+        <v>80.13965486290824</v>
       </c>
       <c r="C68">
-        <v>82.52216593895864</v>
+        <v>93.31879002964905</v>
       </c>
       <c r="D68">
-        <v>91.97064144440066</v>
+        <v>85.47468656738147</v>
       </c>
       <c r="E68">
-        <v>85.25775870091221</v>
+        <v>82.61958477015561</v>
       </c>
       <c r="F68">
-        <v>88.26957560066991</v>
+        <v>85.38817905752359</v>
       </c>
     </row>
     <row r="69">
@@ -1858,19 +1867,19 @@
         </is>
       </c>
       <c r="B69">
-        <v>93.67222364615375</v>
+        <v>47.43323133370231</v>
       </c>
       <c r="C69">
-        <v>95.52639882912496</v>
+        <v>60.13147055314644</v>
       </c>
       <c r="D69">
-        <v>95.10348006162071</v>
+        <v>54.05223958560214</v>
       </c>
       <c r="E69">
-        <v>88.10584526554257</v>
+        <v>52.68246686870511</v>
       </c>
       <c r="F69">
-        <v>93.1019869506105</v>
+        <v>53.574852085289</v>
       </c>
     </row>
     <row r="70">
@@ -1880,19 +1889,19 @@
         </is>
       </c>
       <c r="B70">
-        <v>94.97592531236171</v>
+        <v>86.64348700762194</v>
       </c>
       <c r="C70">
-        <v>91.58813571033716</v>
+        <v>96.90036123375121</v>
       </c>
       <c r="D70">
-        <v>95.776749754628</v>
+        <v>91.06692819273708</v>
       </c>
       <c r="E70">
-        <v>94.81844349635934</v>
+        <v>85.25906877980762</v>
       </c>
       <c r="F70">
-        <v>94.28981356842155</v>
+        <v>89.96746130347947</v>
       </c>
     </row>
     <row r="71">
@@ -1902,19 +1911,19 @@
         </is>
       </c>
       <c r="B71">
-        <v>93.36176908117295</v>
+        <v>67.40091909620999</v>
       </c>
       <c r="C71">
-        <v>86.97445894290222</v>
+        <v>88.36282392010746</v>
       </c>
       <c r="D71">
-        <v>91.46351889542188</v>
+        <v>84.8426914688928</v>
       </c>
       <c r="E71">
-        <v>92.83091314879482</v>
+        <v>73.62388419576641</v>
       </c>
       <c r="F71">
-        <v>91.15766501707297</v>
+        <v>78.55757967024417</v>
       </c>
     </row>
     <row r="72">
@@ -1924,19 +1933,19 @@
         </is>
       </c>
       <c r="B72">
-        <v>93.86375239751038</v>
+        <v>65.74161725477576</v>
       </c>
       <c r="C72">
-        <v>85.28820553780609</v>
+        <v>69.12157454006956</v>
       </c>
       <c r="D72">
-        <v>94.3840755571735</v>
+        <v>68.21541193679474</v>
       </c>
       <c r="E72">
-        <v>12.94624986724835</v>
+        <v>83.67067071470606</v>
       </c>
       <c r="F72">
-        <v>71.62057083993459</v>
+        <v>71.68731861158653</v>
       </c>
     </row>
     <row r="73">
@@ -1946,19 +1955,19 @@
         </is>
       </c>
       <c r="B73">
-        <v>93.32681233697504</v>
+        <v>48.64135313256725</v>
       </c>
       <c r="C73">
-        <v>93.01800686604595</v>
+        <v>65.01443927355302</v>
       </c>
       <c r="D73">
-        <v>91.05503833965513</v>
+        <v>68.19268859532004</v>
       </c>
       <c r="E73">
-        <v>90.58317239757345</v>
+        <v>56.32616035187777</v>
       </c>
       <c r="F73">
-        <v>91.9957574850624</v>
+        <v>59.54366033832952</v>
       </c>
     </row>
     <row r="74">
@@ -1968,19 +1977,19 @@
         </is>
       </c>
       <c r="B74">
-        <v>93.48169270444632</v>
+        <v>68.13197801772628</v>
       </c>
       <c r="C74">
-        <v>91.47532745695726</v>
+        <v>86.68308404896327</v>
       </c>
       <c r="D74">
-        <v>88.95670950801541</v>
+        <v>84.81879192485384</v>
       </c>
       <c r="E74">
-        <v>89.27487305202963</v>
+        <v>75.58708873227512</v>
       </c>
       <c r="F74">
-        <v>90.79715068036215</v>
+        <v>78.80523568095462</v>
       </c>
     </row>
     <row r="75">
@@ -1990,19 +1999,19 @@
         </is>
       </c>
       <c r="B75">
-        <v>95.06471737075131</v>
+        <v>67.46108256857876</v>
       </c>
       <c r="C75">
-        <v>89.89543741863616</v>
+        <v>87.19603689339391</v>
       </c>
       <c r="D75">
-        <v>91.63137883358483</v>
+        <v>79.22865368303928</v>
       </c>
       <c r="E75">
-        <v>90.59882747068701</v>
+        <v>70.2718008136727</v>
       </c>
       <c r="F75">
-        <v>91.79759027341483</v>
+        <v>76.03939348967117</v>
       </c>
     </row>
     <row r="76">
@@ -2012,19 +2021,19 @@
         </is>
       </c>
       <c r="B76">
-        <v>93.19942515608329</v>
+        <v>66.7334550753226</v>
       </c>
       <c r="C76">
-        <v>87.74417215942468</v>
+        <v>83.10630783260279</v>
       </c>
       <c r="D76">
-        <v>89.89193127499748</v>
+        <v>72.79571362354972</v>
       </c>
       <c r="E76">
-        <v>90.60249313108643</v>
+        <v>77.81374518155704</v>
       </c>
       <c r="F76">
-        <v>90.35950543039797</v>
+        <v>75.11230542825804</v>
       </c>
     </row>
     <row r="77">
@@ -2034,19 +2043,19 @@
         </is>
       </c>
       <c r="B77">
-        <v>94.49835896487508</v>
+        <v>60.52846449475501</v>
       </c>
       <c r="C77">
-        <v>92.26405390774325</v>
+        <v>78.73784393613705</v>
       </c>
       <c r="D77">
-        <v>90.71102404754946</v>
+        <v>81.92066602800982</v>
       </c>
       <c r="E77">
-        <v>94.65354999644771</v>
+        <v>51.71282242912078</v>
       </c>
       <c r="F77">
-        <v>93.03174672915387</v>
+        <v>68.22494922200566</v>
       </c>
     </row>
     <row r="78">
@@ -2056,19 +2065,19 @@
         </is>
       </c>
       <c r="B78">
-        <v>92.82319297565756</v>
+        <v>71.60226600337928</v>
       </c>
       <c r="C78">
-        <v>91.07945802985682</v>
+        <v>90.22082169797783</v>
       </c>
       <c r="D78">
-        <v>93.87934857851162</v>
+        <v>88.58803391042358</v>
       </c>
       <c r="E78">
-        <v>114.9332871687148</v>
+        <v>67.98592584311126</v>
       </c>
       <c r="F78">
-        <v>98.17882168818521</v>
+        <v>79.59926186372299</v>
       </c>
     </row>
     <row r="79">
@@ -2078,19 +2087,19 @@
         </is>
       </c>
       <c r="B79">
-        <v>90.97138201369697</v>
+        <v>65.70614182095282</v>
       </c>
       <c r="C79">
-        <v>86.95030152626038</v>
+        <v>80.64348114647809</v>
       </c>
       <c r="D79">
-        <v>94.8011621315194</v>
+        <v>63.87138194409956</v>
       </c>
       <c r="E79">
-        <v>89.28700459209863</v>
+        <v>76.31844778666456</v>
       </c>
       <c r="F79">
-        <v>90.50246256589384</v>
+        <v>71.63486317454876</v>
       </c>
     </row>
     <row r="80">
@@ -2100,19 +2109,19 @@
         </is>
       </c>
       <c r="B80">
-        <v>93.98849554572203</v>
+        <v>49.46087915757376</v>
       </c>
       <c r="C80">
-        <v>83.47151594731434</v>
+        <v>77.29654687039098</v>
       </c>
       <c r="D80">
-        <v>94.97673782156527</v>
+        <v>63.75471090874127</v>
       </c>
       <c r="E80">
-        <v>91.5065519797664</v>
+        <v>74.8262878793567</v>
       </c>
       <c r="F80">
-        <v>90.98582532359201</v>
+        <v>66.33460620401567</v>
       </c>
     </row>
     <row r="81">
@@ -2122,19 +2131,19 @@
         </is>
       </c>
       <c r="B81">
-        <v>93.16102028797992</v>
+        <v>75.44682417949282</v>
       </c>
       <c r="C81">
-        <v>95.38330314009661</v>
+        <v>82.53436713865001</v>
       </c>
       <c r="D81">
-        <v>92.76969226929096</v>
+        <v>85.25248255894462</v>
       </c>
       <c r="E81">
-        <v>90.59272875816986</v>
+        <v>62.38464691342845</v>
       </c>
       <c r="F81">
-        <v>92.97668611388434</v>
+        <v>76.40458019762897</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/1_Data/Aggregates/mean_aggregates.xlsx
+++ b/Data Analysis/1_Data/Aggregates/mean_aggregates.xlsx
@@ -1,21 +1,290 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mm68tulo\Desktop\Jena Chapter\Data Analysis\1_Data\Aggregates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462681D6-1FBB-45AF-8FCF-E7545C6E2B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+  <si>
+    <t>Plotcode</t>
+  </si>
+  <si>
+    <t>mean_spring</t>
+  </si>
+  <si>
+    <t>mean_august</t>
+  </si>
+  <si>
+    <t>mean_november</t>
+  </si>
+  <si>
+    <t>mean_winter</t>
+  </si>
+  <si>
+    <t>B1A01</t>
+  </si>
+  <si>
+    <t>B1A02</t>
+  </si>
+  <si>
+    <t>B1A03</t>
+  </si>
+  <si>
+    <t>B1A04</t>
+  </si>
+  <si>
+    <t>B1A05</t>
+  </si>
+  <si>
+    <t>B1A06</t>
+  </si>
+  <si>
+    <t>B1A07</t>
+  </si>
+  <si>
+    <t>B1A08</t>
+  </si>
+  <si>
+    <t>B1A11</t>
+  </si>
+  <si>
+    <t>B1A12</t>
+  </si>
+  <si>
+    <t>B1A13</t>
+  </si>
+  <si>
+    <t>B1A14</t>
+  </si>
+  <si>
+    <t>B1A15</t>
+  </si>
+  <si>
+    <t>B1A16</t>
+  </si>
+  <si>
+    <t>B1A17</t>
+  </si>
+  <si>
+    <t>B1A18</t>
+  </si>
+  <si>
+    <t>B1A19</t>
+  </si>
+  <si>
+    <t>B1A20</t>
+  </si>
+  <si>
+    <t>B1A21</t>
+  </si>
+  <si>
+    <t>B1A22</t>
+  </si>
+  <si>
+    <t>B2A01</t>
+  </si>
+  <si>
+    <t>B2A02</t>
+  </si>
+  <si>
+    <t>B2A03</t>
+  </si>
+  <si>
+    <t>B2A04</t>
+  </si>
+  <si>
+    <t>B2A05</t>
+  </si>
+  <si>
+    <t>B2A06</t>
+  </si>
+  <si>
+    <t>B2A08</t>
+  </si>
+  <si>
+    <t>B2A09</t>
+  </si>
+  <si>
+    <t>B2A10</t>
+  </si>
+  <si>
+    <t>B2A12</t>
+  </si>
+  <si>
+    <t>B2A13</t>
+  </si>
+  <si>
+    <t>B2A14</t>
+  </si>
+  <si>
+    <t>B2A15</t>
+  </si>
+  <si>
+    <t>B2A16</t>
+  </si>
+  <si>
+    <t>B2A17</t>
+  </si>
+  <si>
+    <t>B2A18</t>
+  </si>
+  <si>
+    <t>B2A19</t>
+  </si>
+  <si>
+    <t>B2A20</t>
+  </si>
+  <si>
+    <t>B2A21</t>
+  </si>
+  <si>
+    <t>B2A22</t>
+  </si>
+  <si>
+    <t>B3A01</t>
+  </si>
+  <si>
+    <t>B3A02</t>
+  </si>
+  <si>
+    <t>B3A03</t>
+  </si>
+  <si>
+    <t>B3A04</t>
+  </si>
+  <si>
+    <t>B3A05</t>
+  </si>
+  <si>
+    <t>B3A06</t>
+  </si>
+  <si>
+    <t>B3A07</t>
+  </si>
+  <si>
+    <t>B3A08</t>
+  </si>
+  <si>
+    <t>B3A09</t>
+  </si>
+  <si>
+    <t>B3A11</t>
+  </si>
+  <si>
+    <t>B3A12</t>
+  </si>
+  <si>
+    <t>B3A13</t>
+  </si>
+  <si>
+    <t>B3A14</t>
+  </si>
+  <si>
+    <t>B3A16</t>
+  </si>
+  <si>
+    <t>B3A17</t>
+  </si>
+  <si>
+    <t>B3A19</t>
+  </si>
+  <si>
+    <t>B3A20</t>
+  </si>
+  <si>
+    <t>B3A21</t>
+  </si>
+  <si>
+    <t>B3A22</t>
+  </si>
+  <si>
+    <t>B3A23</t>
+  </si>
+  <si>
+    <t>B3A24</t>
+  </si>
+  <si>
+    <t>B4A01</t>
+  </si>
+  <si>
+    <t>B4A02</t>
+  </si>
+  <si>
+    <t>B4A04</t>
+  </si>
+  <si>
+    <t>B4A06</t>
+  </si>
+  <si>
+    <t>B4A07</t>
+  </si>
+  <si>
+    <t>B4A08</t>
+  </si>
+  <si>
+    <t>B4A09</t>
+  </si>
+  <si>
+    <t>B4A10</t>
+  </si>
+  <si>
+    <t>B4A11</t>
+  </si>
+  <si>
+    <t>B4A12</t>
+  </si>
+  <si>
+    <t>B4A13</t>
+  </si>
+  <si>
+    <t>B4A14</t>
+  </si>
+  <si>
+    <t>B4A15</t>
+  </si>
+  <si>
+    <t>B4A16</t>
+  </si>
+  <si>
+    <t>B4A17</t>
+  </si>
+  <si>
+    <t>B4A18</t>
+  </si>
+  <si>
+    <t>B4A20</t>
+  </si>
+  <si>
+    <t>B4A21</t>
+  </si>
+  <si>
+    <t>B4A22</t>
+  </si>
+  <si>
+    <t>mean_agg</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,6 +332,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -109,7 +386,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +418,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +470,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,339 +663,299 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F81"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Plotcode</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>mean_spring</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>mean_august</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>mean_november</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mean_winter</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>mean_all</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>B1A01</t>
-        </is>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
       </c>
       <c r="B2">
         <v>93.01248456999177</v>
       </c>
       <c r="C2">
-        <v>91.85646693257752</v>
+        <v>91.856466932577518</v>
       </c>
       <c r="D2">
-        <v>89.31058178202342</v>
+        <v>89.310581782023419</v>
       </c>
       <c r="E2">
-        <v>82.08537438768387</v>
+        <v>82.085374387683871</v>
       </c>
       <c r="F2">
-        <v>89.06622691806915</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B1A02</t>
-        </is>
+        <v>89.066226918069148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>89.23906330682826</v>
+        <v>89.239063306828257</v>
       </c>
       <c r="C3">
-        <v>93.08160104343249</v>
+        <v>93.081601043432485</v>
       </c>
       <c r="D3">
-        <v>87.31555102903747</v>
+        <v>87.315551029037465</v>
       </c>
       <c r="E3">
-        <v>84.03815843811034</v>
+        <v>84.038158438110344</v>
       </c>
       <c r="F3">
-        <v>88.41859345435213</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B1A03</t>
-        </is>
+        <v>88.418593454352134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>79.38450057258757</v>
+        <v>79.384500572587569</v>
       </c>
       <c r="C4">
-        <v>83.85396551373015</v>
+        <v>83.853965513730145</v>
       </c>
       <c r="D4">
-        <v>78.15849929827294</v>
+        <v>78.158499298272943</v>
       </c>
       <c r="E4">
-        <v>66.58765207651281</v>
+        <v>66.587652076512811</v>
       </c>
       <c r="F4">
-        <v>76.99615436527587</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>B1A04</t>
-        </is>
+        <v>76.996154365275871</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>77.70412804911547</v>
+        <v>77.704128049115468</v>
       </c>
       <c r="C5">
-        <v>80.61341435778637</v>
+        <v>80.613414357786368</v>
       </c>
       <c r="D5">
-        <v>71.632834110562</v>
+        <v>71.632834110562001</v>
       </c>
       <c r="E5">
-        <v>72.79483166562015</v>
+        <v>72.794831665620151</v>
       </c>
       <c r="F5">
-        <v>75.686302045771</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>B1A05</t>
-        </is>
+        <v>75.686302045771001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>73.49593344258295</v>
+        <v>73.495933442582952</v>
       </c>
       <c r="C6">
-        <v>83.89931277290763</v>
+        <v>83.899312772907635</v>
       </c>
       <c r="D6">
-        <v>68.70260992217997</v>
+        <v>68.702609922179974</v>
       </c>
       <c r="E6">
-        <v>62.7109311230053</v>
+        <v>62.710931123005302</v>
       </c>
       <c r="F6">
-        <v>72.20219681516896</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>B1A06</t>
-        </is>
+        <v>72.202196815168961</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>89.76616066644301</v>
+        <v>89.766160666443014</v>
       </c>
       <c r="C7">
         <v>93.88966045256204</v>
       </c>
       <c r="D7">
-        <v>87.81214892992988</v>
+        <v>87.812148929929876</v>
       </c>
       <c r="E7">
-        <v>87.12717767756918</v>
+        <v>87.127177677569179</v>
       </c>
       <c r="F7">
-        <v>89.64878693162603</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>B1A07</t>
-        </is>
+        <v>89.648786931626034</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>80.43505971005345</v>
+        <v>80.435059710053451</v>
       </c>
       <c r="C8">
         <v>83.49577747161716</v>
       </c>
       <c r="D8">
-        <v>74.13063828700012</v>
+        <v>74.130638287000124</v>
       </c>
       <c r="E8">
-        <v>61.44498127423068</v>
+        <v>61.444981274230678</v>
       </c>
       <c r="F8">
-        <v>74.87661418572536</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>B1A08</t>
-        </is>
+        <v>74.876614185725359</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
       </c>
       <c r="B9">
         <v>82.36274843971708</v>
       </c>
       <c r="C9">
-        <v>82.77803886852247</v>
+        <v>82.778038868522472</v>
       </c>
       <c r="D9">
-        <v>79.07658431192023</v>
+        <v>79.076584311920229</v>
       </c>
       <c r="E9">
-        <v>66.22142113951092</v>
+        <v>66.221421139510923</v>
       </c>
       <c r="F9">
         <v>77.60969818991768</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>B1A11</t>
-        </is>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>91.33584949321595</v>
+        <v>91.335849493215946</v>
       </c>
       <c r="C10">
-        <v>93.38279276060887</v>
+        <v>93.382792760608865</v>
       </c>
       <c r="D10">
-        <v>87.90097949022423</v>
+        <v>87.900979490224231</v>
       </c>
       <c r="E10">
-        <v>80.25913825375763</v>
+        <v>80.259138253757627</v>
       </c>
       <c r="F10">
-        <v>88.21968999945167</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>B1A12</t>
-        </is>
+        <v>88.219689999451674</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
       </c>
       <c r="B11">
         <v>81.6590782110936</v>
       </c>
       <c r="C11">
-        <v>90.05264660708254</v>
+        <v>90.052646607082536</v>
       </c>
       <c r="D11">
         <v>72.83986492022359</v>
       </c>
       <c r="E11">
-        <v>58.09996674677196</v>
+        <v>58.099966746771962</v>
       </c>
       <c r="F11">
         <v>75.66288912129292</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>B1A13</t>
-        </is>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>74.69791586005874</v>
+        <v>74.697915860058743</v>
       </c>
       <c r="C12">
-        <v>79.53093573317159</v>
+        <v>79.530935733171589</v>
       </c>
       <c r="D12">
-        <v>63.26905561297372</v>
+        <v>63.269055612973723</v>
       </c>
       <c r="E12">
-        <v>70.22196927082189</v>
+        <v>70.221969270821887</v>
       </c>
       <c r="F12">
-        <v>71.92996911925648</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>B1A14</t>
-        </is>
+        <v>71.929969119256484</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
       </c>
       <c r="B13">
         <v>85.51356221262175</v>
       </c>
       <c r="C13">
-        <v>93.82500187931764</v>
+        <v>93.825001879317639</v>
       </c>
       <c r="D13">
-        <v>80.85556440424445</v>
+        <v>80.855564404244447</v>
       </c>
       <c r="E13">
         <v>65.09451149378306</v>
       </c>
       <c r="F13">
-        <v>81.32215999749172</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>B1A15</t>
-        </is>
+        <v>81.322159997491724</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>17</v>
       </c>
       <c r="B14">
-        <v>73.33086064413033</v>
+        <v>73.330860644130325</v>
       </c>
       <c r="C14">
-        <v>75.84277056727844</v>
+        <v>75.842770567278436</v>
       </c>
       <c r="D14">
         <v>60.29006675571636</v>
       </c>
       <c r="E14">
-        <v>68.75179228363662</v>
+        <v>68.751792283636618</v>
       </c>
       <c r="F14">
         <v>69.55387256269043</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>B1A16</t>
-        </is>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>18</v>
       </c>
       <c r="B15">
         <v>82.06243418740236</v>
       </c>
       <c r="C15">
-        <v>90.76102798477611</v>
+        <v>90.761027984776106</v>
       </c>
       <c r="D15">
         <v>70.48474030715613</v>
@@ -691,111 +964,101 @@
         <v>75.56727765308348</v>
       </c>
       <c r="F15">
-        <v>79.71887003310452</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>B1A17</t>
-        </is>
+        <v>79.718870033104523</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>19</v>
       </c>
       <c r="B16">
-        <v>78.25808054478078</v>
+        <v>78.258080544780782</v>
       </c>
       <c r="C16">
-        <v>86.07639561406238</v>
+        <v>86.076395614062378</v>
       </c>
       <c r="D16">
-        <v>67.76155792522397</v>
+        <v>67.761557925223968</v>
       </c>
       <c r="E16">
         <v>72.57229819576375</v>
       </c>
       <c r="F16">
-        <v>76.16708306995773</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>B1A18</t>
-        </is>
+        <v>76.167083069957727</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>20</v>
       </c>
       <c r="B17">
-        <v>81.08714738479897</v>
+        <v>81.087147384798968</v>
       </c>
       <c r="C17">
         <v>87.00421345953923</v>
       </c>
       <c r="D17">
-        <v>77.27419697290156</v>
+        <v>77.274196972901564</v>
       </c>
       <c r="E17">
-        <v>61.33233312294647</v>
+        <v>61.332333122946473</v>
       </c>
       <c r="F17">
         <v>76.67447273504655</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>B1A19</t>
-        </is>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>21</v>
       </c>
       <c r="B18">
-        <v>85.04347816239522</v>
+        <v>85.043478162395218</v>
       </c>
       <c r="C18">
-        <v>92.11632128700984</v>
+        <v>92.116321287009839</v>
       </c>
       <c r="D18">
         <v>54.98779394950725</v>
       </c>
       <c r="E18">
-        <v>82.4195140840517</v>
+        <v>82.419514084051698</v>
       </c>
       <c r="F18">
-        <v>78.641776870741</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>B1A20</t>
-        </is>
+        <v>78.641776870740998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>22</v>
       </c>
       <c r="B19">
-        <v>86.35859071724538</v>
+        <v>86.358590717245377</v>
       </c>
       <c r="C19">
-        <v>95.21625530095518</v>
+        <v>95.216255300955183</v>
       </c>
       <c r="D19">
-        <v>84.75473407010391</v>
+        <v>84.754734070103908</v>
       </c>
       <c r="E19">
-        <v>79.66412214225799</v>
+        <v>79.664122142257995</v>
       </c>
       <c r="F19">
-        <v>86.49842555764062</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>B1A21</t>
-        </is>
+        <v>86.498425557640616</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>23</v>
       </c>
       <c r="B20">
-        <v>80.22119980799626</v>
+        <v>80.221199807996257</v>
       </c>
       <c r="C20">
         <v>86.83103000767413</v>
       </c>
       <c r="D20">
-        <v>71.06840817194764</v>
+        <v>71.068408171947638</v>
       </c>
       <c r="E20">
         <v>71.70088553349899</v>
@@ -804,215 +1067,195 @@
         <v>77.45538088027925</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>B1A22</t>
-        </is>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>24</v>
       </c>
       <c r="B21">
-        <v>92.8920144296831</v>
+        <v>92.892014429683101</v>
       </c>
       <c r="C21">
-        <v>96.51070451899095</v>
+        <v>96.510704518990948</v>
       </c>
       <c r="D21">
-        <v>87.89858562517507</v>
+        <v>87.898585625175073</v>
       </c>
       <c r="E21">
-        <v>89.88318102504942</v>
+        <v>89.883181025049424</v>
       </c>
       <c r="F21">
         <v>91.79612139972464</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>B2A01</t>
-        </is>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>25</v>
       </c>
       <c r="B22">
-        <v>92.63729475231575</v>
+        <v>92.637294752315753</v>
       </c>
       <c r="C22">
-        <v>91.86171422225493</v>
+        <v>91.861714222254932</v>
       </c>
       <c r="D22">
-        <v>89.15060889267784</v>
+        <v>89.150608892677838</v>
       </c>
       <c r="E22">
         <v>80.67632678528777</v>
       </c>
       <c r="F22">
-        <v>88.58148616313407</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>B2A02</t>
-        </is>
+        <v>88.581486163134073</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>26</v>
       </c>
       <c r="B23">
-        <v>87.09476246426441</v>
+        <v>87.094762464264406</v>
       </c>
       <c r="C23">
-        <v>89.51432485355815</v>
+        <v>89.514324853558151</v>
       </c>
       <c r="D23">
-        <v>79.97847991839377</v>
+        <v>79.978479918393774</v>
       </c>
       <c r="E23">
-        <v>82.58658112658624</v>
+        <v>82.586581126586239</v>
       </c>
       <c r="F23">
-        <v>84.79353709070064</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>B2A03</t>
-        </is>
+        <v>84.793537090700639</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>27</v>
       </c>
       <c r="B24">
-        <v>94.72684871681533</v>
+        <v>94.726848716815326</v>
       </c>
       <c r="C24">
-        <v>94.83542297602357</v>
+        <v>94.835422976023565</v>
       </c>
       <c r="D24">
-        <v>87.91004927773876</v>
+        <v>87.910049277738764</v>
       </c>
       <c r="E24">
-        <v>81.32630320238293</v>
+        <v>81.326303202382931</v>
       </c>
       <c r="F24">
         <v>89.69965604324014</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>B2A04</t>
-        </is>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>28</v>
       </c>
       <c r="B25">
-        <v>67.28152804079583</v>
+        <v>67.281528040795834</v>
       </c>
       <c r="C25">
-        <v>73.56129883008599</v>
+        <v>73.561298830085988</v>
       </c>
       <c r="D25">
-        <v>63.77266104720584</v>
+        <v>63.772661047205837</v>
       </c>
       <c r="E25">
         <v>46.77266627177513</v>
       </c>
       <c r="F25">
-        <v>62.8470385474657</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>B2A05</t>
-        </is>
+        <v>62.847038547465701</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>29</v>
       </c>
       <c r="B26">
-        <v>79.20994005244516</v>
+        <v>79.209940052445162</v>
       </c>
       <c r="C26">
-        <v>80.37713769636889</v>
+        <v>80.377137696368891</v>
       </c>
       <c r="D26">
         <v>76.79137456111529</v>
       </c>
       <c r="E26">
-        <v>63.97541833013832</v>
+        <v>63.975418330138318</v>
       </c>
       <c r="F26">
-        <v>75.08846766001692</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>B2A06</t>
-        </is>
+        <v>75.088467660016917</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>30</v>
       </c>
       <c r="B27">
-        <v>87.94211538188448</v>
+        <v>87.942115381884477</v>
       </c>
       <c r="C27">
-        <v>92.52671411342173</v>
+        <v>92.526714113421733</v>
       </c>
       <c r="D27">
-        <v>85.34693503441214</v>
+        <v>85.346935034412141</v>
       </c>
       <c r="E27">
-        <v>74.61337774721326</v>
+        <v>74.613377747213264</v>
       </c>
       <c r="F27">
         <v>85.1072855692329</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>B2A08</t>
-        </is>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>31</v>
       </c>
       <c r="B28">
-        <v>78.60623867414972</v>
+        <v>78.606238674149722</v>
       </c>
       <c r="C28">
-        <v>86.81592962449845</v>
+        <v>86.815929624498452</v>
       </c>
       <c r="D28">
-        <v>79.09703869111426</v>
+        <v>79.097038691114264</v>
       </c>
       <c r="E28">
-        <v>71.80616276502157</v>
+        <v>71.806162765021568</v>
       </c>
       <c r="F28">
-        <v>79.081342438696</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>B2A09</t>
-        </is>
+        <v>79.081342438695998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>32</v>
       </c>
       <c r="B29">
-        <v>90.23541532623952</v>
+        <v>90.235415326239519</v>
       </c>
       <c r="C29">
         <v>93.19005166119554</v>
       </c>
       <c r="D29">
-        <v>80.60139977284035</v>
+        <v>80.601399772840352</v>
       </c>
       <c r="E29">
-        <v>88.77346470201267</v>
+        <v>88.773464702012674</v>
       </c>
       <c r="F29">
-        <v>88.20008286557203</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>B2A10</t>
-        </is>
+        <v>88.200082865572028</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>33</v>
       </c>
       <c r="B30">
-        <v>91.28364300331502</v>
+        <v>91.283643003315021</v>
       </c>
       <c r="C30">
-        <v>92.88118402007422</v>
+        <v>92.881184020074215</v>
       </c>
       <c r="D30">
         <v>92.04572562706646</v>
@@ -1021,680 +1264,618 @@
         <v>89.5727374866498</v>
       </c>
       <c r="F30">
-        <v>91.44582253427637</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>B2A12</t>
-        </is>
+        <v>91.445822534276374</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>34</v>
       </c>
       <c r="B31">
         <v>90.18068935509595</v>
       </c>
       <c r="C31">
-        <v>95.69653686486595</v>
+        <v>95.696536864865948</v>
       </c>
       <c r="D31">
-        <v>91.95804825023805</v>
+        <v>91.958048250238051</v>
       </c>
       <c r="E31">
-        <v>81.34573955774218</v>
+        <v>81.345739557742178</v>
       </c>
       <c r="F31">
-        <v>89.79525350698553</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>B2A13</t>
-        </is>
+        <v>89.795253506985532</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>35</v>
       </c>
       <c r="B32">
-        <v>87.03966451469306</v>
+        <v>87.039664514693058</v>
       </c>
       <c r="C32">
-        <v>91.81027046216387</v>
+        <v>91.810270462163871</v>
       </c>
       <c r="D32">
-        <v>81.05528042490798</v>
+        <v>81.055280424907977</v>
       </c>
       <c r="E32">
-        <v>82.11794370706778</v>
+        <v>82.117943707067781</v>
       </c>
       <c r="F32">
-        <v>85.50578977720818</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>B2A14</t>
-        </is>
+        <v>85.505789777208179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>36</v>
       </c>
       <c r="B33">
-        <v>88.00535105626322</v>
+        <v>88.005351056263223</v>
       </c>
       <c r="C33">
         <v>93.34907408976737</v>
       </c>
       <c r="D33">
-        <v>80.05776593474327</v>
+        <v>80.057765934743273</v>
       </c>
       <c r="E33">
-        <v>82.14688092718039</v>
+        <v>82.146880927180391</v>
       </c>
       <c r="F33">
-        <v>85.88976800198856</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>B2A15</t>
-        </is>
+        <v>85.889768001988557</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>37</v>
       </c>
       <c r="B34">
-        <v>68.93229334481777</v>
+        <v>68.932293344817765</v>
       </c>
       <c r="C34">
-        <v>84.00816040985477</v>
+        <v>84.008160409854767</v>
       </c>
       <c r="D34">
-        <v>62.36555832243543</v>
+        <v>62.365558322435433</v>
       </c>
       <c r="E34">
-        <v>535.3277706119746</v>
+        <v>535.32777061197464</v>
       </c>
       <c r="F34">
-        <v>187.6584456722707</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>B2A16</t>
-        </is>
+        <v>187.65844567227069</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>38</v>
       </c>
       <c r="B35">
-        <v>89.85966947950421</v>
+        <v>89.859669479504205</v>
       </c>
       <c r="C35">
-        <v>89.94708590230563</v>
+        <v>89.947085902305631</v>
       </c>
       <c r="D35">
-        <v>87.74016380206895</v>
+        <v>87.740163802068949</v>
       </c>
       <c r="E35">
-        <v>81.45035709608518</v>
+        <v>81.450357096085185</v>
       </c>
       <c r="F35">
-        <v>87.24931906999099</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>B2A17</t>
-        </is>
+        <v>87.249319069990989</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>39</v>
       </c>
       <c r="B36">
-        <v>85.60157727236876</v>
+        <v>85.601577272368758</v>
       </c>
       <c r="C36">
-        <v>92.09941673393742</v>
+        <v>92.099416733937417</v>
       </c>
       <c r="D36">
-        <v>83.36368704065673</v>
+        <v>83.363687040656728</v>
       </c>
       <c r="E36">
-        <v>76.07326426982718</v>
+        <v>76.073264269827177</v>
       </c>
       <c r="F36">
         <v>84.28448632919752</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>B2A18</t>
-        </is>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>40</v>
       </c>
       <c r="B37">
-        <v>91.80182009111071</v>
+        <v>91.801820091110713</v>
       </c>
       <c r="C37">
-        <v>95.20228923158454</v>
+        <v>95.202289231584544</v>
       </c>
       <c r="D37">
-        <v>82.42344418527232</v>
+        <v>82.423444185272317</v>
       </c>
       <c r="E37">
         <v>68.44811404031536</v>
       </c>
       <c r="F37">
-        <v>84.46891688707073</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>B2A19</t>
-        </is>
+        <v>84.468916887070733</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>41</v>
       </c>
       <c r="B38">
-        <v>82.54219351014117</v>
+        <v>82.542193510141175</v>
       </c>
       <c r="C38">
         <v>84.66848750652737</v>
       </c>
       <c r="D38">
-        <v>79.73502237736238</v>
+        <v>79.735022377362384</v>
       </c>
       <c r="E38">
-        <v>73.60475891698815</v>
+        <v>73.604758916988146</v>
       </c>
       <c r="F38">
-        <v>80.13761557775477</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>B2A20</t>
-        </is>
+        <v>80.137615577754772</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>42</v>
       </c>
       <c r="B39">
-        <v>85.51866041342365</v>
+        <v>85.518660413423646</v>
       </c>
       <c r="C39">
-        <v>91.49605755036089</v>
+        <v>91.496057550360888</v>
       </c>
       <c r="D39">
-        <v>83.60823163965453</v>
+        <v>83.608231639654534</v>
       </c>
       <c r="E39">
-        <v>80.40800779490188</v>
+        <v>80.408007794901877</v>
       </c>
       <c r="F39">
-        <v>85.25773934958524</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>B2A21</t>
-        </is>
+        <v>85.257739349585236</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>43</v>
       </c>
       <c r="B40">
-        <v>93.56534954885821</v>
+        <v>93.565349548858208</v>
       </c>
       <c r="C40">
-        <v>92.84067771193726</v>
+        <v>92.840677711937261</v>
       </c>
       <c r="D40">
-        <v>85.99067069411666</v>
+        <v>85.990670694116659</v>
       </c>
       <c r="E40">
-        <v>93.20083081575166</v>
+        <v>93.200830815751658</v>
       </c>
       <c r="F40">
-        <v>91.39938219266594</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>B2A22</t>
-        </is>
+        <v>91.399382192665939</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>44</v>
       </c>
       <c r="B41">
-        <v>92.83284952124363</v>
+        <v>92.832849521243631</v>
       </c>
       <c r="C41">
-        <v>96.35464948078942</v>
+        <v>96.354649480789419</v>
       </c>
       <c r="D41">
-        <v>85.3563192926302</v>
+        <v>85.356319292630204</v>
       </c>
       <c r="E41">
-        <v>86.78155523354744</v>
+        <v>86.781555233547437</v>
       </c>
       <c r="F41">
-        <v>90.33134338205267</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>B3A01</t>
-        </is>
+        <v>90.331343382052665</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>45</v>
       </c>
       <c r="B42">
-        <v>72.12356763406567</v>
+        <v>72.123567634065665</v>
       </c>
       <c r="C42">
-        <v>92.01772519250767</v>
+        <v>92.017725192507669</v>
       </c>
       <c r="D42">
-        <v>62.81230232449741</v>
+        <v>62.812302324497409</v>
       </c>
       <c r="E42">
-        <v>67.69082109540875</v>
+        <v>67.690821095408751</v>
       </c>
       <c r="F42">
-        <v>73.66110406161988</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>B3A02</t>
-        </is>
+        <v>73.661104061619881</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>46</v>
       </c>
       <c r="B43">
-        <v>68.25289691588546</v>
+        <v>68.252896915885458</v>
       </c>
       <c r="C43">
-        <v>84.41774506187849</v>
+        <v>84.417745061878492</v>
       </c>
       <c r="D43">
-        <v>73.86233178823582</v>
+        <v>73.862331788235821</v>
       </c>
       <c r="E43">
-        <v>69.894930116219</v>
+        <v>69.894930116219001</v>
       </c>
       <c r="F43">
-        <v>74.10697597055469</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>B3A03</t>
-        </is>
+        <v>74.106975970554686</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>47</v>
       </c>
       <c r="B44">
-        <v>67.75960871741746</v>
+        <v>67.759608717417464</v>
       </c>
       <c r="C44">
-        <v>84.90881233496653</v>
+        <v>84.908812334966527</v>
       </c>
       <c r="D44">
-        <v>78.80573929689854</v>
+        <v>78.805739296898537</v>
       </c>
       <c r="E44">
-        <v>64.62654842424627</v>
+        <v>64.626548424246266</v>
       </c>
       <c r="F44">
-        <v>74.02517719338221</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>B3A04</t>
-        </is>
+        <v>74.025177193382206</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>48</v>
       </c>
       <c r="B45">
         <v>80.34712453251548</v>
       </c>
       <c r="C45">
-        <v>94.16819666380239</v>
+        <v>94.168196663802391</v>
       </c>
       <c r="D45">
-        <v>83.84345164645339</v>
+        <v>83.843451646453389</v>
       </c>
       <c r="E45">
-        <v>71.51922269055619</v>
+        <v>71.519222690556191</v>
       </c>
       <c r="F45">
-        <v>82.46949888333187</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>B3A05</t>
-        </is>
+        <v>82.469498883331866</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>49</v>
       </c>
       <c r="B46">
-        <v>84.77512605263074</v>
+        <v>84.775126052630739</v>
       </c>
       <c r="C46">
         <v>94.72225840518378</v>
       </c>
       <c r="D46">
-        <v>89.3503560244036</v>
+        <v>89.350356024403595</v>
       </c>
       <c r="E46">
-        <v>81.87461536186075</v>
+        <v>81.874615361860748</v>
       </c>
       <c r="F46">
-        <v>87.68058896101971</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>B3A06</t>
-        </is>
+        <v>87.680588961019708</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>50</v>
       </c>
       <c r="B47">
-        <v>71.66311767374461</v>
+        <v>71.663117673744608</v>
       </c>
       <c r="C47">
-        <v>90.66693737575137</v>
+        <v>90.666937375751374</v>
       </c>
       <c r="D47">
-        <v>79.68216705466554</v>
+        <v>79.682167054665541</v>
       </c>
       <c r="E47">
-        <v>74.63576383475589</v>
+        <v>74.635763834755892</v>
       </c>
       <c r="F47">
-        <v>79.16199648472936</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>B3A07</t>
-        </is>
+        <v>79.161996484729357</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>51</v>
       </c>
       <c r="B48">
-        <v>88.80318241092375</v>
+        <v>88.803182410923753</v>
       </c>
       <c r="C48">
-        <v>95.25462453064358</v>
+        <v>95.254624530643582</v>
       </c>
       <c r="D48">
-        <v>90.42271505426186</v>
+        <v>90.422715054261857</v>
       </c>
       <c r="E48">
-        <v>75.3823168574428</v>
+        <v>75.382316857442802</v>
       </c>
       <c r="F48">
-        <v>87.46570971331801</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>B3A08</t>
-        </is>
+        <v>87.465709713318006</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>52</v>
       </c>
       <c r="B49">
-        <v>63.12249067659924</v>
+        <v>63.122490676599242</v>
       </c>
       <c r="C49">
-        <v>77.89012302780702</v>
+        <v>77.890123027807022</v>
       </c>
       <c r="D49">
-        <v>66.56292156804228</v>
+        <v>66.562921568042285</v>
       </c>
       <c r="E49">
-        <v>54.97369422524827</v>
+        <v>54.973694225248273</v>
       </c>
       <c r="F49">
-        <v>65.63730737442421</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>B3A09</t>
-        </is>
+        <v>65.637307374424211</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>53</v>
       </c>
       <c r="B50">
-        <v>86.66379868947546</v>
+        <v>86.663798689475456</v>
       </c>
       <c r="C50">
-        <v>97.17286503423196</v>
+        <v>97.172865034231961</v>
       </c>
       <c r="D50">
-        <v>92.97795410309318</v>
+        <v>92.977954103093182</v>
       </c>
       <c r="E50">
-        <v>90.69655227623812</v>
+        <v>90.696552276238123</v>
       </c>
       <c r="F50">
-        <v>91.87779252575967</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>B3A11</t>
-        </is>
+        <v>91.877792525759673</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>54</v>
       </c>
       <c r="B51">
-        <v>93.69547617961024</v>
+        <v>93.695476179610239</v>
       </c>
       <c r="C51">
-        <v>97.68562843375862</v>
+        <v>97.685628433758623</v>
       </c>
       <c r="D51">
-        <v>92.87461176891681</v>
+        <v>92.874611768916807</v>
       </c>
       <c r="E51">
-        <v>93.62155317155869</v>
+        <v>93.621553171558688</v>
       </c>
       <c r="F51">
-        <v>94.46931738846109</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>B3A12</t>
-        </is>
+        <v>94.469317388461093</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>55</v>
       </c>
       <c r="B52">
-        <v>73.78221228001905</v>
+        <v>73.782212280019053</v>
       </c>
       <c r="C52">
-        <v>90.5794508806196</v>
+        <v>90.579450880619603</v>
       </c>
       <c r="D52">
-        <v>82.52580077623963</v>
+        <v>82.525800776239635</v>
       </c>
       <c r="E52">
         <v>87.36116476006562</v>
       </c>
       <c r="F52">
-        <v>83.56215717423598</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>B3A13</t>
-        </is>
+        <v>83.562157174235978</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>56</v>
       </c>
       <c r="B53">
-        <v>85.37462946723386</v>
+        <v>85.374629467233859</v>
       </c>
       <c r="C53">
-        <v>94.90627595418279</v>
+        <v>94.906275954182789</v>
       </c>
       <c r="D53">
-        <v>85.09704142676999</v>
+        <v>85.097041426769991</v>
       </c>
       <c r="E53">
         <v>499.2671504360211</v>
       </c>
       <c r="F53">
-        <v>191.1612743210519</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>B3A14</t>
-        </is>
+        <v>191.16127432105191</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>57</v>
       </c>
       <c r="B54">
-        <v>86.62894747199034</v>
+        <v>86.628947471990344</v>
       </c>
       <c r="C54">
-        <v>94.77405842685368</v>
+        <v>94.774058426853685</v>
       </c>
       <c r="D54">
-        <v>87.43021783363868</v>
+        <v>87.430217833638679</v>
       </c>
       <c r="E54">
-        <v>87.0685284562723</v>
+        <v>87.068528456272304</v>
       </c>
       <c r="F54">
         <v>88.97543804718876</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>B3A16</t>
-        </is>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>58</v>
       </c>
       <c r="B55">
-        <v>71.59201895184468</v>
+        <v>71.592018951844679</v>
       </c>
       <c r="C55">
-        <v>86.88809230825434</v>
+        <v>86.888092308254343</v>
       </c>
       <c r="D55">
-        <v>79.75859602068137</v>
+        <v>79.758596020681367</v>
       </c>
       <c r="E55">
-        <v>80.03037067958917</v>
+        <v>80.030370679589169</v>
       </c>
       <c r="F55">
-        <v>79.56726949009239</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>B3A17</t>
-        </is>
+        <v>79.567269490092386</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>59</v>
       </c>
       <c r="B56">
-        <v>61.91987466807181</v>
+        <v>61.919874668071813</v>
       </c>
       <c r="C56">
-        <v>79.85725810014482</v>
+        <v>79.857258100144819</v>
       </c>
       <c r="D56">
-        <v>59.88619215390431</v>
+        <v>59.886192153904311</v>
       </c>
       <c r="E56">
-        <v>58.31585700406149</v>
+        <v>58.315857004061492</v>
       </c>
       <c r="F56">
-        <v>64.99479548154561</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>B3A19</t>
-        </is>
+        <v>64.994795481545609</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>60</v>
       </c>
       <c r="B57">
-        <v>80.63505101146414</v>
+        <v>80.635051011464142</v>
       </c>
       <c r="C57">
-        <v>88.1503506802281</v>
+        <v>88.150350680228101</v>
       </c>
       <c r="D57">
-        <v>85.88053126491623</v>
+        <v>85.880531264916229</v>
       </c>
       <c r="E57">
-        <v>68.58719180004974</v>
+        <v>68.587191800049737</v>
       </c>
       <c r="F57">
-        <v>80.81328118916456</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>B3A20</t>
-        </is>
+        <v>80.813281189164556</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>61</v>
       </c>
       <c r="B58">
-        <v>89.5611963664156</v>
+        <v>89.561196366415601</v>
       </c>
       <c r="C58">
-        <v>93.91580607224655</v>
+        <v>93.915806072246554</v>
       </c>
       <c r="D58">
-        <v>84.95020457637592</v>
+        <v>84.950204576375924</v>
       </c>
       <c r="E58">
-        <v>68.71693183831331</v>
+        <v>68.716931838313315</v>
       </c>
       <c r="F58">
-        <v>84.28603471333784</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>B3A21</t>
-        </is>
+        <v>84.286034713337841</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>62</v>
       </c>
       <c r="B59">
-        <v>70.44222318113925</v>
+        <v>70.442223181139255</v>
       </c>
       <c r="C59">
-        <v>86.04918909655608</v>
+        <v>86.049189096556077</v>
       </c>
       <c r="D59">
-        <v>74.58169032050336</v>
+        <v>74.581690320503355</v>
       </c>
       <c r="E59">
-        <v>72.71809813220172</v>
+        <v>72.718098132201717</v>
       </c>
       <c r="F59">
-        <v>75.9478001826001</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>B3A22</t>
-        </is>
+        <v>75.947800182600105</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>63</v>
       </c>
       <c r="B60">
-        <v>90.71279536603899</v>
+        <v>90.712795366038989</v>
       </c>
       <c r="C60">
-        <v>96.68437041140264</v>
+        <v>96.684370411402639</v>
       </c>
       <c r="D60">
-        <v>95.41303142259657</v>
+        <v>95.413031422596575</v>
       </c>
       <c r="E60">
-        <v>84.86583535015939</v>
+        <v>84.865835350159387</v>
       </c>
       <c r="F60">
-        <v>91.9190081375494</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>B3A23</t>
-        </is>
+        <v>91.919008137549397</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>64</v>
       </c>
       <c r="B61">
-        <v>87.85408793102306</v>
+        <v>87.854087931023059</v>
       </c>
       <c r="C61">
-        <v>95.66832587893968</v>
+        <v>95.668325878939683</v>
       </c>
       <c r="D61">
         <v>94.07047539894613</v>
@@ -1706,193 +1887,175 @@
         <v>91.4321148288806</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>B3A24</t>
-        </is>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>65</v>
       </c>
       <c r="B62">
-        <v>90.92992743566791</v>
+        <v>90.929927435667906</v>
       </c>
       <c r="C62">
-        <v>97.81696401280955</v>
+        <v>97.816964012809549</v>
       </c>
       <c r="D62">
-        <v>95.20543491168719</v>
+        <v>95.205434911687192</v>
       </c>
       <c r="E62">
-        <v>88.94042972658768</v>
+        <v>88.940429726587681</v>
       </c>
       <c r="F62">
-        <v>93.22318902168809</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>B4A01</t>
-        </is>
+        <v>93.223189021688086</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>66</v>
       </c>
       <c r="B63">
-        <v>121.6426254491709</v>
+        <v>121.64262544917089</v>
       </c>
       <c r="C63">
-        <v>97.96578846454715</v>
+        <v>97.965788464547146</v>
       </c>
       <c r="D63">
-        <v>94.72310225195521</v>
+        <v>94.723102251955211</v>
       </c>
       <c r="E63">
-        <v>94.62862305636656</v>
+        <v>94.628623056366564</v>
       </c>
       <c r="F63">
-        <v>102.2400348055099</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>B4A02</t>
-        </is>
+        <v>102.24003480550989</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>67</v>
       </c>
       <c r="B64">
-        <v>89.3097706277216</v>
+        <v>89.309770627721605</v>
       </c>
       <c r="C64">
-        <v>96.16304990005881</v>
+        <v>96.163049900058809</v>
       </c>
       <c r="D64">
-        <v>96.8312472837888</v>
+        <v>96.831247283788798</v>
       </c>
       <c r="E64">
-        <v>93.04655588727415</v>
+        <v>93.046555887274152</v>
       </c>
       <c r="F64">
-        <v>93.83765592471084</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>B4A04</t>
-        </is>
+        <v>93.837655924710845</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>68</v>
       </c>
       <c r="B65">
         <v>78.24948254041324</v>
       </c>
       <c r="C65">
-        <v>96.14893884769133</v>
+        <v>96.148938847691326</v>
       </c>
       <c r="D65">
-        <v>95.02568235298695</v>
+        <v>95.025682352986948</v>
       </c>
       <c r="E65">
-        <v>82.50234585023425</v>
+        <v>82.502345850234249</v>
       </c>
       <c r="F65">
-        <v>87.98161239783144</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>B4A06</t>
-        </is>
+        <v>87.981612397831441</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>69</v>
       </c>
       <c r="B66">
-        <v>78.10706440388719</v>
+        <v>78.107064403887193</v>
       </c>
       <c r="C66">
-        <v>92.45196196462184</v>
+        <v>92.451961964621844</v>
       </c>
       <c r="D66">
-        <v>89.59396009466117</v>
+        <v>89.593960094661171</v>
       </c>
       <c r="E66">
         <v>88.08467732857757</v>
       </c>
       <c r="F66">
-        <v>87.05941594793694</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>B4A07</t>
-        </is>
+        <v>87.059415947936941</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>70</v>
       </c>
       <c r="B67">
-        <v>63.82617044238492</v>
+        <v>63.826170442384921</v>
       </c>
       <c r="C67">
-        <v>85.58816124913834</v>
+        <v>85.588161249138338</v>
       </c>
       <c r="D67">
-        <v>73.34394169053471</v>
+        <v>73.343941690534706</v>
       </c>
       <c r="E67">
-        <v>73.18057206249799</v>
+        <v>73.180572062497987</v>
       </c>
       <c r="F67">
-        <v>73.98471136113899</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>B4A08</t>
-        </is>
+        <v>73.984711361138991</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>71</v>
       </c>
       <c r="B68">
-        <v>80.13965486290824</v>
+        <v>80.139654862908245</v>
       </c>
       <c r="C68">
-        <v>93.31879002964905</v>
+        <v>93.318790029649051</v>
       </c>
       <c r="D68">
-        <v>85.47468656738147</v>
+        <v>85.474686567381468</v>
       </c>
       <c r="E68">
-        <v>82.61958477015561</v>
+        <v>82.619584770155612</v>
       </c>
       <c r="F68">
-        <v>85.38817905752359</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>B4A09</t>
-        </is>
+        <v>85.388179057523587</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>72</v>
       </c>
       <c r="B69">
-        <v>47.43323133370231</v>
+        <v>47.433231333702309</v>
       </c>
       <c r="C69">
-        <v>60.13147055314644</v>
+        <v>60.131470553146443</v>
       </c>
       <c r="D69">
-        <v>54.05223958560214</v>
+        <v>54.052239585602138</v>
       </c>
       <c r="E69">
-        <v>52.68246686870511</v>
+        <v>52.682466868705113</v>
       </c>
       <c r="F69">
-        <v>53.574852085289</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>B4A10</t>
-        </is>
+        <v>53.574852085289002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>73</v>
       </c>
       <c r="B70">
-        <v>86.64348700762194</v>
+        <v>86.643487007621943</v>
       </c>
       <c r="C70">
-        <v>96.90036123375121</v>
+        <v>96.900361233751212</v>
       </c>
       <c r="D70">
         <v>91.06692819273708</v>
@@ -1901,249 +2064,227 @@
         <v>85.25906877980762</v>
       </c>
       <c r="F70">
-        <v>89.96746130347947</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>B4A11</t>
-        </is>
+        <v>89.967461303479467</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>74</v>
       </c>
       <c r="B71">
-        <v>67.40091909620999</v>
+        <v>67.400919096209989</v>
       </c>
       <c r="C71">
-        <v>88.36282392010746</v>
+        <v>88.362823920107459</v>
       </c>
       <c r="D71">
-        <v>84.8426914688928</v>
+        <v>84.842691468892795</v>
       </c>
       <c r="E71">
-        <v>73.62388419576641</v>
+        <v>73.623884195766408</v>
       </c>
       <c r="F71">
-        <v>78.55757967024417</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>B4A12</t>
-        </is>
+        <v>78.557579670244166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>75</v>
       </c>
       <c r="B72">
-        <v>65.74161725477576</v>
+        <v>65.741617254775761</v>
       </c>
       <c r="C72">
         <v>69.12157454006956</v>
       </c>
       <c r="D72">
-        <v>68.21541193679474</v>
+        <v>68.215411936794737</v>
       </c>
       <c r="E72">
-        <v>83.67067071470606</v>
+        <v>83.670670714706063</v>
       </c>
       <c r="F72">
-        <v>71.68731861158653</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>B4A13</t>
-        </is>
+        <v>71.687318611586534</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>76</v>
       </c>
       <c r="B73">
-        <v>48.64135313256725</v>
+        <v>48.641353132567247</v>
       </c>
       <c r="C73">
-        <v>65.01443927355302</v>
+        <v>65.014439273553023</v>
       </c>
       <c r="D73">
-        <v>68.19268859532004</v>
+        <v>68.192688595320035</v>
       </c>
       <c r="E73">
-        <v>56.32616035187777</v>
+        <v>56.326160351877768</v>
       </c>
       <c r="F73">
-        <v>59.54366033832952</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>B4A14</t>
-        </is>
+        <v>59.543660338329524</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>77</v>
       </c>
       <c r="B74">
-        <v>68.13197801772628</v>
+        <v>68.131978017726283</v>
       </c>
       <c r="C74">
-        <v>86.68308404896327</v>
+        <v>86.683084048963266</v>
       </c>
       <c r="D74">
-        <v>84.81879192485384</v>
+        <v>84.818791924853841</v>
       </c>
       <c r="E74">
         <v>75.58708873227512</v>
       </c>
       <c r="F74">
-        <v>78.80523568095462</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>B4A15</t>
-        </is>
+        <v>78.805235680954624</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>78</v>
       </c>
       <c r="B75">
         <v>67.46108256857876</v>
       </c>
       <c r="C75">
-        <v>87.19603689339391</v>
+        <v>87.196036893393909</v>
       </c>
       <c r="D75">
-        <v>79.22865368303928</v>
+        <v>79.228653683039283</v>
       </c>
       <c r="E75">
-        <v>70.2718008136727</v>
+        <v>70.271800813672698</v>
       </c>
       <c r="F75">
         <v>76.03939348967117</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>B4A16</t>
-        </is>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>79</v>
       </c>
       <c r="B76">
-        <v>66.7334550753226</v>
+        <v>66.733455075322595</v>
       </c>
       <c r="C76">
-        <v>83.10630783260279</v>
+        <v>83.106307832602795</v>
       </c>
       <c r="D76">
-        <v>72.79571362354972</v>
+        <v>72.795713623549716</v>
       </c>
       <c r="E76">
-        <v>77.81374518155704</v>
+        <v>77.813745181557039</v>
       </c>
       <c r="F76">
         <v>75.11230542825804</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>B4A17</t>
-        </is>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>80</v>
       </c>
       <c r="B77">
-        <v>60.52846449475501</v>
+        <v>60.528464494755013</v>
       </c>
       <c r="C77">
-        <v>78.73784393613705</v>
+        <v>78.737843936137054</v>
       </c>
       <c r="D77">
-        <v>81.92066602800982</v>
+        <v>81.920666028009819</v>
       </c>
       <c r="E77">
-        <v>51.71282242912078</v>
+        <v>51.712822429120777</v>
       </c>
       <c r="F77">
-        <v>68.22494922200566</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>B4A18</t>
-        </is>
+        <v>68.224949222005662</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>81</v>
       </c>
       <c r="B78">
-        <v>71.60226600337928</v>
+        <v>71.602266003379285</v>
       </c>
       <c r="C78">
-        <v>90.22082169797783</v>
+        <v>90.220821697977826</v>
       </c>
       <c r="D78">
-        <v>88.58803391042358</v>
+        <v>88.588033910423576</v>
       </c>
       <c r="E78">
-        <v>67.98592584311126</v>
+        <v>67.985925843111261</v>
       </c>
       <c r="F78">
-        <v>79.59926186372299</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>B4A20</t>
-        </is>
+        <v>79.599261863722987</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>82</v>
       </c>
       <c r="B79">
-        <v>65.70614182095282</v>
+        <v>65.706141820952823</v>
       </c>
       <c r="C79">
-        <v>80.64348114647809</v>
+        <v>80.643481146478095</v>
       </c>
       <c r="D79">
-        <v>63.87138194409956</v>
+        <v>63.871381944099561</v>
       </c>
       <c r="E79">
-        <v>76.31844778666456</v>
+        <v>76.318447786664564</v>
       </c>
       <c r="F79">
-        <v>71.63486317454876</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>B4A21</t>
-        </is>
+        <v>71.634863174548755</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>83</v>
       </c>
       <c r="B80">
-        <v>49.46087915757376</v>
+        <v>49.460879157573757</v>
       </c>
       <c r="C80">
-        <v>77.29654687039098</v>
+        <v>77.296546870390983</v>
       </c>
       <c r="D80">
-        <v>63.75471090874127</v>
+        <v>63.754710908741266</v>
       </c>
       <c r="E80">
-        <v>74.8262878793567</v>
+        <v>74.826287879356698</v>
       </c>
       <c r="F80">
-        <v>66.33460620401567</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>B4A22</t>
-        </is>
+        <v>66.334606204015671</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>84</v>
       </c>
       <c r="B81">
-        <v>75.44682417949282</v>
+        <v>75.446824179492822</v>
       </c>
       <c r="C81">
-        <v>82.53436713865001</v>
+        <v>82.534367138650012</v>
       </c>
       <c r="D81">
-        <v>85.25248255894462</v>
+        <v>85.252482558944621</v>
       </c>
       <c r="E81">
-        <v>62.38464691342845</v>
+        <v>62.384646913428448</v>
       </c>
       <c r="F81">
-        <v>76.40458019762897</v>
+        <v>76.404580197628974</v>
       </c>
     </row>
   </sheetData>
